--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.71 ± 0.06</t>
+          <t>0.68 ± 0.06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.64 ± 0.05</t>
+          <t>0.59 ± 0.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.67 ± 0.16</t>
+          <t>0.67 ± 0.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.21</t>
+          <t>0.57 ± 0.22</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.59 ± 0.17</t>
+          <t>0.57 ± 0.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.70 ± 0.14</t>
+          <t>0.79 ± 0.12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F4" t="n">
